--- a/docs/architecture/eterna_ipcamera_architecture.xlsx
+++ b/docs/architecture/eterna_ipcamera_architecture.xlsx
@@ -14,6 +14,7 @@
     <sheet name="Startup Sequence" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Configuration" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="Singleton Inventory" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Concurrency &amp; Safety" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Overview'!$A$1:$H$28</definedName>
@@ -25,7 +26,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="18">
+  <fonts count="21">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -131,8 +132,26 @@
       <color rgb="004A4A4A"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001B2A4A"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00C0392B"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="0027AE60"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="18">
+  <fills count="19">
     <fill>
       <patternFill/>
     </fill>
@@ -219,6 +238,11 @@
         <fgColor rgb="00FADBD8"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00922B21"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="7">
     <border>
@@ -295,7 +319,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="78">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -488,6 +512,36 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -5067,4 +5121,1669 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00922B21"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J65"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="52" customWidth="1" min="5" max="5"/>
+    <col width="46" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="B1" s="68" t="inlineStr">
+        <is>
+          <t>Concurrency &amp; Thread-Safety Analysis</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  THREAD INVENTORY</t>
+        </is>
+      </c>
+      <c r="B2" s="7" t="n"/>
+      <c r="C2" s="7" t="n"/>
+      <c r="D2" s="7" t="n"/>
+      <c r="E2" s="7" t="n"/>
+      <c r="F2" s="8" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr"/>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>Thread</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>Purpose</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>Shutdown mechanism</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="16" t="inlineStr"/>
+      <c r="B4" s="69" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="C4" s="16" t="inlineStr">
+        <is>
+          <t>main.cpp</t>
+        </is>
+      </c>
+      <c r="D4" s="16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E4" s="16" t="inlineStr">
+        <is>
+          <t>Signal-wait loop; startup/shutdown coordinator</t>
+        </is>
+      </c>
+      <c r="F4" s="16" t="inlineStr">
+        <is>
+          <t>SIGTERM → g_running=false</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="19" t="inlineStr"/>
+      <c r="B5" s="70" t="inlineStr">
+        <is>
+          <t>ProducerThread</t>
+        </is>
+      </c>
+      <c r="C5" s="19" t="inlineStr">
+        <is>
+          <t>MediaHub</t>
+        </is>
+      </c>
+      <c r="D5" s="19" t="inlineStr">
+        <is>
+          <t>1 per active channel (max 4)</t>
+        </is>
+      </c>
+      <c r="E5" s="19" t="inlineStr">
+        <is>
+          <t>Pulls encoded frames from HDAL; writes to ring buffer</t>
+        </is>
+      </c>
+      <c r="F5" s="19" t="inlineStr">
+        <is>
+          <t>stop_requested.store(true) + join()</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="16" t="inlineStr"/>
+      <c r="B6" s="69" t="inlineStr">
+        <is>
+          <t>ProcessingThread</t>
+        </is>
+      </c>
+      <c r="C6" s="16" t="inlineStr">
+        <is>
+          <t>EventManager</t>
+        </is>
+      </c>
+      <c r="D6" s="16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E6" s="16" t="inlineStr">
+        <is>
+          <t>Single consumer of event queue; dispatches rules and listeners</t>
+        </is>
+      </c>
+      <c r="F6" s="16" t="inlineStr">
+        <is>
+          <t>running_=false + notify_all + join()</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="19" t="inlineStr"/>
+      <c r="B7" s="70" t="inlineStr">
+        <is>
+          <t>Action threads</t>
+        </is>
+      </c>
+      <c r="C7" s="19" t="inlineStr">
+        <is>
+          <t>EventManager</t>
+        </is>
+      </c>
+      <c r="D7" s="19" t="inlineStr">
+        <is>
+          <t>N (detached)</t>
+        </is>
+      </c>
+      <c r="E7" s="19" t="inlineStr">
+        <is>
+          <t>One per triggered action (recording, email, webhook, MQTT, FTP, I/O)</t>
+        </is>
+      </c>
+      <c r="F7" s="19" t="inlineStr">
+        <is>
+          <t>Detached — no explicit drain (known risk R2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="16" t="inlineStr"/>
+      <c r="B8" s="69" t="inlineStr">
+        <is>
+          <t>ProcessingThread</t>
+        </is>
+      </c>
+      <c r="C8" s="16" t="inlineStr">
+        <is>
+          <t>AnalyticsEngine</t>
+        </is>
+      </c>
+      <c r="D8" s="16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E8" s="16" t="inlineStr">
+        <is>
+          <t>Main AI inference loop (NPU + object tracking)</t>
+        </is>
+      </c>
+      <c r="F8" s="16" t="inlineStr">
+        <is>
+          <t>running_.store(false) + join()</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="19" t="inlineStr"/>
+      <c r="B9" s="70" t="inlineStr">
+        <is>
+          <t>MdProcessingThread</t>
+        </is>
+      </c>
+      <c r="C9" s="19" t="inlineStr">
+        <is>
+          <t>AnalyticsEngine</t>
+        </is>
+      </c>
+      <c r="D9" s="19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E9" s="19" t="inlineStr">
+        <is>
+          <t>Motion detection on 160×120 YUV path</t>
+        </is>
+      </c>
+      <c r="F9" s="19" t="inlineStr">
+        <is>
+          <t>md_thread_running_.store(false) + join()</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="16" t="inlineStr"/>
+      <c r="B10" s="69" t="inlineStr">
+        <is>
+          <t>AudioProcessingThread</t>
+        </is>
+      </c>
+      <c r="C10" s="16" t="inlineStr">
+        <is>
+          <t>AnalyticsEngine</t>
+        </is>
+      </c>
+      <c r="D10" s="16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E10" s="16" t="inlineStr">
+        <is>
+          <t>Audio classification</t>
+        </is>
+      </c>
+      <c r="F10" s="16" t="inlineStr">
+        <is>
+          <t>audio_thread_running_.store(false) + join()</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="19" t="inlineStr"/>
+      <c r="B11" s="70" t="inlineStr">
+        <is>
+          <t>RecordingThread</t>
+        </is>
+      </c>
+      <c r="C11" s="19" t="inlineStr">
+        <is>
+          <t>RecordingService</t>
+        </is>
+      </c>
+      <c r="D11" s="19" t="inlineStr">
+        <is>
+          <t>1 per active channel</t>
+        </is>
+      </c>
+      <c r="E11" s="19" t="inlineStr">
+        <is>
+          <t>MP4 write loop; consumes from MediaHub ring buffer</t>
+        </is>
+      </c>
+      <c r="F11" s="19" t="inlineStr">
+        <is>
+          <t>stop_requested=true + join()</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="16" t="inlineStr"/>
+      <c r="B12" s="69" t="inlineStr">
+        <is>
+          <t>MonitorThread</t>
+        </is>
+      </c>
+      <c r="C12" s="16" t="inlineStr">
+        <is>
+          <t>RecordingService</t>
+        </is>
+      </c>
+      <c r="D12" s="16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E12" s="16" t="inlineStr">
+        <is>
+          <t>Polls SD card availability every 5 s</t>
+        </is>
+      </c>
+      <c r="F12" s="16" t="inlineStr">
+        <is>
+          <t>shutdown_requested_=true + join()</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="19" t="inlineStr"/>
+      <c r="B13" s="70" t="inlineStr">
+        <is>
+          <t>UploadWorker</t>
+        </is>
+      </c>
+      <c r="C13" s="19" t="inlineStr">
+        <is>
+          <t>FtpManager</t>
+        </is>
+      </c>
+      <c r="D13" s="19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E13" s="19" t="inlineStr">
+        <is>
+          <t>Queued FTP upload processing (libcurl)</t>
+        </is>
+      </c>
+      <c r="F13" s="19" t="inlineStr">
+        <is>
+          <t>shutdown_requested_.store(true) + notify_all + join()</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="16" t="inlineStr"/>
+      <c r="B14" s="69" t="inlineStr">
+        <is>
+          <t>AutoDetectionLoop</t>
+        </is>
+      </c>
+      <c r="C14" s="16" t="inlineStr">
+        <is>
+          <t>IRControl</t>
+        </is>
+      </c>
+      <c r="D14" s="16" t="inlineStr">
+        <is>
+          <t>0 or 1</t>
+        </is>
+      </c>
+      <c r="E14" s="16" t="inlineStr">
+        <is>
+          <t>Luma-threshold day/night switching</t>
+        </is>
+      </c>
+      <c r="F14" s="16" t="inlineStr">
+        <is>
+          <t>auto_thread_running_.store(false) + notify_all + join()</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="19" t="inlineStr"/>
+      <c r="B15" s="70" t="inlineStr">
+        <is>
+          <t>ScheduleMonitorLoop</t>
+        </is>
+      </c>
+      <c r="C15" s="19" t="inlineStr">
+        <is>
+          <t>IRControl</t>
+        </is>
+      </c>
+      <c r="D15" s="19" t="inlineStr">
+        <is>
+          <t>0 or 1</t>
+        </is>
+      </c>
+      <c r="E15" s="19" t="inlineStr">
+        <is>
+          <t>Time-based day/night schedule</t>
+        </is>
+      </c>
+      <c r="F15" s="19" t="inlineStr">
+        <is>
+          <t>schedule_thread_running_.store(false) + notify_all + join()</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1">
+      <c r="A16" s="16" t="inlineStr"/>
+      <c r="B16" s="69" t="inlineStr">
+        <is>
+          <t>SwCdsDetectionLoop</t>
+        </is>
+      </c>
+      <c r="C16" s="16" t="inlineStr">
+        <is>
+          <t>IRControl</t>
+        </is>
+      </c>
+      <c r="D16" s="16" t="inlineStr">
+        <is>
+          <t>0 or 1</t>
+        </is>
+      </c>
+      <c r="E16" s="16" t="inlineStr">
+        <is>
+          <t>Software CDS (ISP EV-value) day/night detection</t>
+        </is>
+      </c>
+      <c r="F16" s="16" t="inlineStr">
+        <is>
+          <t>sw_cds_thread_running_.store(false) + notify_all + join()</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1">
+      <c r="A17" s="19" t="inlineStr"/>
+      <c r="B17" s="70" t="inlineStr">
+        <is>
+          <t>Live555 event loop</t>
+        </is>
+      </c>
+      <c r="C17" s="19" t="inlineStr">
+        <is>
+          <t>RtspServer</t>
+        </is>
+      </c>
+      <c r="D17" s="19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E17" s="19" t="inlineStr">
+        <is>
+          <t>Single-threaded RTSP/RTP dispatch (Live555 framework)</t>
+        </is>
+      </c>
+      <c r="F17" s="19" t="inlineStr">
+        <is>
+          <t>live555::Medium::close()</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="30" customHeight="1">
+      <c r="A18" s="16" t="inlineStr"/>
+      <c r="B18" s="69" t="inlineStr">
+        <is>
+          <t>Link monitor</t>
+        </is>
+      </c>
+      <c r="C18" s="16" t="inlineStr">
+        <is>
+          <t>NetworkManager</t>
+        </is>
+      </c>
+      <c r="D18" s="16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E18" s="16" t="inlineStr">
+        <is>
+          <t>Periodic interface link-state polling</t>
+        </is>
+      </c>
+      <c r="F18" s="16" t="inlineStr">
+        <is>
+          <t>Atomic flag + join()</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="30" customHeight="1">
+      <c r="A19" s="19" t="inlineStr"/>
+      <c r="B19" s="70" t="inlineStr">
+        <is>
+          <t>SystemLogger worker</t>
+        </is>
+      </c>
+      <c r="C19" s="19" t="inlineStr">
+        <is>
+          <t>SystemLogger</t>
+        </is>
+      </c>
+      <c r="D19" s="19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E19" s="19" t="inlineStr">
+        <is>
+          <t>Periodic dmesg/temp/stats collection</t>
+        </is>
+      </c>
+      <c r="F19" s="19" t="inlineStr">
+        <is>
+          <t>Atomic flag + join()</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  KEY CONCURRENCY MECHANISMS</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="n"/>
+      <c r="C21" s="7" t="n"/>
+      <c r="D21" s="7" t="n"/>
+      <c r="E21" s="7" t="n"/>
+      <c r="F21" s="8" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr"/>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>Mechanism</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>Where</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>Pattern</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>Race Condition Prevented</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="70" customHeight="1">
+      <c r="A23" s="16" t="inlineStr"/>
+      <c r="B23" s="15" t="inlineStr">
+        <is>
+          <t>Seqlock-style ring buffer</t>
+        </is>
+      </c>
+      <c r="C23" s="16" t="inlineStr">
+        <is>
+          <t>MediaHub
+media_hub.cpp</t>
+        </is>
+      </c>
+      <c r="D23" s="17" t="inlineStr">
+        <is>
+          <t>atomic&lt;uint64_t&gt; version per slot
+Odd = writing, Even = ready
+Release store / Acquire load</t>
+        </is>
+      </c>
+      <c r="E23" s="16" t="inlineStr">
+        <is>
+          <t>Torn reads of encoded video frames by multiple concurrent consumers</t>
+        </is>
+      </c>
+      <c r="F23" s="16" t="inlineStr">
+        <is>
+          <t>No mutex on read path — lock-free SPMC.
+Trailing re-read catches overwrites that started mid-memcpy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="70" customHeight="1">
+      <c r="A24" s="19" t="inlineStr"/>
+      <c r="B24" s="18" t="inlineStr">
+        <is>
+          <t>False-sharing prevention</t>
+        </is>
+      </c>
+      <c r="C24" s="19" t="inlineStr">
+        <is>
+          <t>MediaHub
+media_hub.h</t>
+        </is>
+      </c>
+      <c r="D24" s="20" t="inlineStr">
+        <is>
+          <t>alignas(64) on write_pos_ and frames_written_</t>
+        </is>
+      </c>
+      <c r="E24" s="19" t="inlineStr">
+        <is>
+          <t>Cache-line ping-pong between producer writes and consumer reads on multi-core SoC</t>
+        </is>
+      </c>
+      <c r="F24" s="19" t="inlineStr">
+        <is>
+          <t>Avoids cache-line invalidation on every frame written.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="70" customHeight="1">
+      <c r="A25" s="16" t="inlineStr"/>
+      <c r="B25" s="15" t="inlineStr">
+        <is>
+          <t>Atomic pause/resume for codec change</t>
+        </is>
+      </c>
+      <c r="C25" s="16" t="inlineStr">
+        <is>
+          <t>MediaHub
+VideoControl</t>
+        </is>
+      </c>
+      <c r="D25" s="17" t="inlineStr">
+        <is>
+          <t>paused.store(true, release) → HDAL param change → paused.store(false, release)
+frame_mutex guards cached_sps/pps/vps</t>
+        </is>
+      </c>
+      <c r="E25" s="16" t="inlineStr">
+        <is>
+          <t>ProducerThread accessing HDAL encoder handle while parameters are being changed</t>
+        </is>
+      </c>
+      <c r="F25" s="16" t="inlineStr">
+        <is>
+          <t>PauseChannel sleeps kVideoPullTimeoutMs+50ms to let producer exit any in-progress HDAL call before the change.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="70" customHeight="1">
+      <c r="A26" s="19" t="inlineStr"/>
+      <c r="B26" s="18" t="inlineStr">
+        <is>
+          <t>running_.exchange for idempotent stop</t>
+        </is>
+      </c>
+      <c r="C26" s="19" t="inlineStr">
+        <is>
+          <t>MediaHub</t>
+        </is>
+      </c>
+      <c r="D26" s="20" t="inlineStr">
+        <is>
+          <t>running_.exchange(false, memory_order_release)</t>
+        </is>
+      </c>
+      <c r="E26" s="19" t="inlineStr">
+        <is>
+          <t>Two concurrent Stop() calls: both attempt to join producer threads</t>
+        </is>
+      </c>
+      <c r="F26" s="19" t="inlineStr">
+        <is>
+          <t>exchange atomically reads-and-clears — only effective stopper triggers the join path.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="70" customHeight="1">
+      <c r="A27" s="16" t="inlineStr"/>
+      <c r="B27" s="15" t="inlineStr">
+        <is>
+          <t>Copy-before-iterate (listeners)</t>
+        </is>
+      </c>
+      <c r="C27" s="16" t="inlineStr">
+        <is>
+          <t>EventManager
+event_manager.cpp</t>
+        </is>
+      </c>
+      <c r="D27" s="17" t="inlineStr">
+        <is>
+          <t>Copy listeners_ under lock, release lock, iterate copy</t>
+        </is>
+      </c>
+      <c r="E27" s="16" t="inlineStr">
+        <is>
+          <t>Deadlock: listener callback calling AddListener/RemoveListener which acquires listeners_mutex_</t>
+        </is>
+      </c>
+      <c r="F27" s="16" t="inlineStr">
+        <is>
+          <t>Trade-off: a listener removed mid-iteration receives one final notification.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="70" customHeight="1">
+      <c r="A28" s="19" t="inlineStr"/>
+      <c r="B28" s="18" t="inlineStr">
+        <is>
+          <t>Lock released before callbacks</t>
+        </is>
+      </c>
+      <c r="C28" s="19" t="inlineStr">
+        <is>
+          <t>AnalyticsEngine
+IRControl
+RecordingService</t>
+        </is>
+      </c>
+      <c r="D28" s="20" t="inlineStr">
+        <is>
+          <t>Narrow lock scope for stats update; callback fired after scope closes</t>
+        </is>
+      </c>
+      <c r="E28" s="19" t="inlineStr">
+        <is>
+          <t>Deadlock: callback re-entering any method that acquires the same non-recursive mutex_</t>
+        </is>
+      </c>
+      <c r="F28" s="19" t="inlineStr">
+        <is>
+          <t>Pattern applied to 7 of 8 analytics callbacks. audio_event_callback_ is an exception (Risk R3).</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="70" customHeight="1">
+      <c r="A29" s="16" t="inlineStr"/>
+      <c r="B29" s="15" t="inlineStr">
+        <is>
+          <t>unique_lock.unlock() before re-entrant call</t>
+        </is>
+      </c>
+      <c r="C29" s="16" t="inlineStr">
+        <is>
+          <t>HdalPipeline
+IRControl</t>
+        </is>
+      </c>
+      <c r="D29" s="17" t="inlineStr">
+        <is>
+          <t>unique_lock lock(mutex); ...; lock.unlock(); CallFuncThatAcquiresMutex(); lock.lock();</t>
+        </is>
+      </c>
+      <c r="E29" s="16" t="inlineStr">
+        <is>
+          <t>Deadlock from non-recursive std::mutex + call chain that re-acquires the same lock</t>
+        </is>
+      </c>
+      <c r="F29" s="16" t="inlineStr">
+        <is>
+          <t>Rollback path re-acquires the lock via a fresh lock_guard.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="70" customHeight="1">
+      <c r="A30" s="19" t="inlineStr"/>
+      <c r="B30" s="18" t="inlineStr">
+        <is>
+          <t>Shutdown() defers lock until after Stop()</t>
+        </is>
+      </c>
+      <c r="C30" s="19" t="inlineStr">
+        <is>
+          <t>HdalPipeline</t>
+        </is>
+      </c>
+      <c r="D30" s="20" t="inlineStr">
+        <is>
+          <t>Shutdown() calls Stop() (which locks), then acquires lock for cleanup</t>
+        </is>
+      </c>
+      <c r="E30" s="19" t="inlineStr">
+        <is>
+          <t>Deadlock: Shutdown holding lock → calls Stop() → tries to acquire same lock</t>
+        </is>
+      </c>
+      <c r="F30" s="19" t="inlineStr">
+        <is>
+          <t>Explicitly commented in source.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="70" customHeight="1">
+      <c r="A31" s="16" t="inlineStr"/>
+      <c r="B31" s="15" t="inlineStr">
+        <is>
+          <t>Interruptible sleep via condition_variable</t>
+        </is>
+      </c>
+      <c r="C31" s="16" t="inlineStr">
+        <is>
+          <t>IRControl
+FtpManager
+RecordingService</t>
+        </is>
+      </c>
+      <c r="D31" s="17" t="inlineStr">
+        <is>
+          <t>cv.wait_for(lock, timeout, [this]{ return stop_flag.load(); })
+cv.notify_all() in Shutdown()</t>
+        </is>
+      </c>
+      <c r="E31" s="16" t="inlineStr">
+        <is>
+          <t>Up to 30-second join delay if thread uses plain sleep_for(30s)</t>
+        </is>
+      </c>
+      <c r="F31" s="16" t="inlineStr">
+        <is>
+          <t>RecordingService MonitorThread uses 50×100ms chunked sleep instead.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="70" customHeight="1">
+      <c r="A32" s="19" t="inlineStr"/>
+      <c r="B32" s="18" t="inlineStr">
+        <is>
+          <t>Thread join as happens-before fence</t>
+        </is>
+      </c>
+      <c r="C32" s="19" t="inlineStr">
+        <is>
+          <t>MediaHub, AnalyticsEngine
+EventManager, FtpManager, IRControl</t>
+        </is>
+      </c>
+      <c r="D32" s="20" t="inlineStr">
+        <is>
+          <t>flag.store(false); thread.join(); // then access shared resources</t>
+        </is>
+      </c>
+      <c r="E32" s="19" t="inlineStr">
+        <is>
+          <t>Use-after-free of HDAL VB pool pages; concurrent MD engine access; in-flight curl transfer during cleanup</t>
+        </is>
+      </c>
+      <c r="F32" s="19" t="inlineStr">
+        <is>
+          <t>All join sites guarded with joinable() to prevent UB from joining a non-joinable thread.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="70" customHeight="1">
+      <c r="A33" s="16" t="inlineStr"/>
+      <c r="B33" s="15" t="inlineStr">
+        <is>
+          <t>Atomic rename() for file safety</t>
+        </is>
+      </c>
+      <c r="C33" s="16" t="inlineStr">
+        <is>
+          <t>Config module
+NetworkManager</t>
+        </is>
+      </c>
+      <c r="D33" s="17" t="inlineStr">
+        <is>
+          <t>write to .tmp → rename() atomically replaces target</t>
+        </is>
+      </c>
+      <c r="E33" s="16" t="inlineStr">
+        <is>
+          <t>Partial-write corruption: reader sees truncated JSON or certificate on crash/power loss</t>
+        </is>
+      </c>
+      <c r="F33" s="16" t="inlineStr">
+        <is>
+          <t>POSIX guarantees rename() on same filesystem is atomic.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="70" customHeight="1">
+      <c r="A34" s="19" t="inlineStr"/>
+      <c r="B34" s="18" t="inlineStr">
+        <is>
+          <t>force_segment_cut acq_rel exchange</t>
+        </is>
+      </c>
+      <c r="C34" s="19" t="inlineStr">
+        <is>
+          <t>RecordingService</t>
+        </is>
+      </c>
+      <c r="D34" s="20" t="inlineStr">
+        <is>
+          <t>store(true, release); exchange(false, acq_rel)</t>
+        </is>
+      </c>
+      <c r="E34" s="19" t="inlineStr">
+        <is>
+          <t>Double-cut: two CutNow() calls resulting in two segments being cut; missed preceding encoder-settings writes</t>
+        </is>
+      </c>
+      <c r="F34" s="19" t="inlineStr">
+        <is>
+          <t>Release on store ensures codec-change writes visible; acq_rel exchange atomically reads-and-clears.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  MUTEX HIERARCHY &amp; LOCK ORDERING</t>
+        </is>
+      </c>
+      <c r="B36" s="7" t="n"/>
+      <c r="C36" s="7" t="n"/>
+      <c r="D36" s="7" t="n"/>
+      <c r="E36" s="7" t="n"/>
+      <c r="F36" s="8" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr"/>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>Module</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>Mutex / Lock</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>Protects</t>
+        </is>
+      </c>
+      <c r="E37" s="6" t="inlineStr">
+        <is>
+          <t>Lock-ordering constraint</t>
+        </is>
+      </c>
+      <c r="F37" s="6" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="40" customHeight="1">
+      <c r="A38" s="16" t="inlineStr"/>
+      <c r="B38" s="69" t="inlineStr">
+        <is>
+          <t>Config</t>
+        </is>
+      </c>
+      <c r="C38" s="16" t="inlineStr">
+        <is>
+          <t>g_mutex (anon ns)</t>
+        </is>
+      </c>
+      <c r="D38" s="16" t="inlineStr">
+        <is>
+          <t>g_config_tree, g_factory_tree, g_cache, g_initialized</t>
+        </is>
+      </c>
+      <c r="E38" s="16" t="inlineStr">
+        <is>
+          <t>None — sole lock in module</t>
+        </is>
+      </c>
+      <c r="F38" s="16" t="inlineStr"/>
+    </row>
+    <row r="39" ht="40" customHeight="1">
+      <c r="A39" s="19" t="inlineStr"/>
+      <c r="B39" s="70" t="inlineStr">
+        <is>
+          <t>HdalPipeline</t>
+        </is>
+      </c>
+      <c r="C39" s="19" t="inlineStr">
+        <is>
+          <t>g_pipeline_mutex (global)</t>
+        </is>
+      </c>
+      <c r="D39" s="19" t="inlineStr">
+        <is>
+          <t>All HDAL path handles, stream configs, encoder state</t>
+        </is>
+      </c>
+      <c r="E39" s="19" t="inlineStr">
+        <is>
+          <t>None — sole lock in module</t>
+        </is>
+      </c>
+      <c r="F39" s="19" t="inlineStr">
+        <is>
+          <t>unique_lock.unlock() before ReinitWithConfig()</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="40" customHeight="1">
+      <c r="A40" s="16" t="inlineStr"/>
+      <c r="B40" s="69" t="inlineStr">
+        <is>
+          <t>IRControl</t>
+        </is>
+      </c>
+      <c r="C40" s="16" t="inlineStr">
+        <is>
+          <t>g_mutex (anon ns)</t>
+        </is>
+      </c>
+      <c r="D40" s="16" t="inlineStr">
+        <is>
+          <t>ir_led_settings_, ir_cut_settings_, auto_settings_, is_night_mode_, callbacks</t>
+        </is>
+      </c>
+      <c r="E40" s="16" t="inlineStr">
+        <is>
+          <t>None — sole lock in module</t>
+        </is>
+      </c>
+      <c r="F40" s="16" t="inlineStr">
+        <is>
+          <t>Manual unlock before SwitchTo*() calls</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="40" customHeight="1">
+      <c r="A41" s="19" t="inlineStr"/>
+      <c r="B41" s="70" t="inlineStr">
+        <is>
+          <t>MediaHub</t>
+        </is>
+      </c>
+      <c r="C41" s="19" t="inlineStr">
+        <is>
+          <t>frame_mutex (per channel)</t>
+        </is>
+      </c>
+      <c r="D41" s="19" t="inlineStr">
+        <is>
+          <t>cached_sps/pps/vps, cached_codec; pairs with frame_cv</t>
+        </is>
+      </c>
+      <c r="E41" s="19" t="inlineStr">
+        <is>
+          <t>None — sole lock per channel</t>
+        </is>
+      </c>
+      <c r="F41" s="19" t="inlineStr"/>
+    </row>
+    <row r="42" ht="40" customHeight="1">
+      <c r="A42" s="16" t="inlineStr"/>
+      <c r="B42" s="69" t="inlineStr">
+        <is>
+          <t>EventManager</t>
+        </is>
+      </c>
+      <c r="C42" s="16" t="inlineStr">
+        <is>
+          <t>queue_mutex_</t>
+        </is>
+      </c>
+      <c r="D42" s="16" t="inlineStr">
+        <is>
+          <t>event_queue_</t>
+        </is>
+      </c>
+      <c r="E42" s="16" t="inlineStr">
+        <is>
+          <t>queue_mutex_ must never be held when acquiring others</t>
+        </is>
+      </c>
+      <c r="F42" s="16" t="inlineStr"/>
+    </row>
+    <row r="43" ht="40" customHeight="1">
+      <c r="A43" s="19" t="inlineStr"/>
+      <c r="B43" s="70" t="inlineStr">
+        <is>
+          <t>EventManager</t>
+        </is>
+      </c>
+      <c r="C43" s="19" t="inlineStr">
+        <is>
+          <t>rules_mutex_</t>
+        </is>
+      </c>
+      <c r="D43" s="19" t="inlineStr">
+        <is>
+          <t>rules_ vector</t>
+        </is>
+      </c>
+      <c r="E43" s="19" t="inlineStr">
+        <is>
+          <t>Independent of queue_mutex_</t>
+        </is>
+      </c>
+      <c r="F43" s="19" t="inlineStr">
+        <is>
+          <t>Raw pointer escape from MatchRules() — Risk R3</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="40" customHeight="1">
+      <c r="A44" s="16" t="inlineStr"/>
+      <c r="B44" s="69" t="inlineStr">
+        <is>
+          <t>EventManager</t>
+        </is>
+      </c>
+      <c r="C44" s="16" t="inlineStr">
+        <is>
+          <t>listeners_mutex_</t>
+        </is>
+      </c>
+      <c r="D44" s="16" t="inlineStr">
+        <is>
+          <t>listeners_ vector</t>
+        </is>
+      </c>
+      <c r="E44" s="16" t="inlineStr">
+        <is>
+          <t>Independent of queue_mutex_</t>
+        </is>
+      </c>
+      <c r="F44" s="16" t="inlineStr">
+        <is>
+          <t>Copy-before-iterate to prevent deadlock on re-entrant callbacks</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="40" customHeight="1">
+      <c r="A45" s="19" t="inlineStr"/>
+      <c r="B45" s="70" t="inlineStr">
+        <is>
+          <t>EventManager</t>
+        </is>
+      </c>
+      <c r="C45" s="19" t="inlineStr">
+        <is>
+          <t>config_mutex_</t>
+        </is>
+      </c>
+      <c r="D45" s="19" t="inlineStr">
+        <is>
+          <t>EventManagerConfig struct</t>
+        </is>
+      </c>
+      <c r="E45" s="19" t="inlineStr">
+        <is>
+          <t>config_mutex_ → rules_mutex_ (in LoadConfig)</t>
+        </is>
+      </c>
+      <c r="F45" s="19" t="inlineStr"/>
+    </row>
+    <row r="46" ht="40" customHeight="1">
+      <c r="A46" s="16" t="inlineStr"/>
+      <c r="B46" s="69" t="inlineStr">
+        <is>
+          <t>EventManager</t>
+        </is>
+      </c>
+      <c r="C46" s="16" t="inlineStr">
+        <is>
+          <t>history_mutex_</t>
+        </is>
+      </c>
+      <c r="D46" s="16" t="inlineStr">
+        <is>
+          <t>event_history_ deque</t>
+        </is>
+      </c>
+      <c r="E46" s="16" t="inlineStr">
+        <is>
+          <t>Independent</t>
+        </is>
+      </c>
+      <c r="F46" s="16" t="inlineStr"/>
+    </row>
+    <row r="47" ht="40" customHeight="1">
+      <c r="A47" s="19" t="inlineStr"/>
+      <c r="B47" s="70" t="inlineStr">
+        <is>
+          <t>EventManager</t>
+        </is>
+      </c>
+      <c r="C47" s="19" t="inlineStr">
+        <is>
+          <t>stats_mutex_</t>
+        </is>
+      </c>
+      <c r="D47" s="19" t="inlineStr">
+        <is>
+          <t>EventStats struct + maps</t>
+        </is>
+      </c>
+      <c r="E47" s="19" t="inlineStr">
+        <is>
+          <t>Independent — also acquired inside detached action threads</t>
+        </is>
+      </c>
+      <c r="F47" s="19" t="inlineStr"/>
+    </row>
+    <row r="48" ht="40" customHeight="1">
+      <c r="A48" s="16" t="inlineStr"/>
+      <c r="B48" s="69" t="inlineStr">
+        <is>
+          <t>AnalyticsEngine</t>
+        </is>
+      </c>
+      <c r="C48" s="16" t="inlineStr">
+        <is>
+          <t>mutex_ (instance)</t>
+        </is>
+      </c>
+      <c r="D48" s="16" t="inlineStr">
+        <is>
+          <t>config_, stats_, all 8 callback members</t>
+        </is>
+      </c>
+      <c r="E48" s="16" t="inlineStr">
+        <is>
+          <t>None — sole lock in class</t>
+        </is>
+      </c>
+      <c r="F48" s="16" t="inlineStr">
+        <is>
+          <t>Do NOT hold during callbacks — deadlock risk</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="40" customHeight="1">
+      <c r="A49" s="19" t="inlineStr"/>
+      <c r="B49" s="70" t="inlineStr">
+        <is>
+          <t>RecordingService</t>
+        </is>
+      </c>
+      <c r="C49" s="19" t="inlineStr">
+        <is>
+          <t>config_mutex_</t>
+        </is>
+      </c>
+      <c r="D49" s="19" t="inlineStr">
+        <is>
+          <t>RecordingConfig, channel configs</t>
+        </is>
+      </c>
+      <c r="E49" s="19" t="inlineStr">
+        <is>
+          <t>config_mutex_ → callback_mutex_ (in TryReconnectStorage)</t>
+        </is>
+      </c>
+      <c r="F49" s="19" t="inlineStr"/>
+    </row>
+    <row r="50" ht="40" customHeight="1">
+      <c r="A50" s="16" t="inlineStr"/>
+      <c r="B50" s="69" t="inlineStr">
+        <is>
+          <t>RecordingService</t>
+        </is>
+      </c>
+      <c r="C50" s="16" t="inlineStr">
+        <is>
+          <t>callback_mutex_</t>
+        </is>
+      </c>
+      <c r="D50" s="16" t="inlineStr">
+        <is>
+          <t>segment_callback_, status_callback_, storage_callback_</t>
+        </is>
+      </c>
+      <c r="E50" s="16" t="inlineStr">
+        <is>
+          <t>Must be acquired AFTER config_mutex_ if both needed</t>
+        </is>
+      </c>
+      <c r="F50" s="16" t="inlineStr"/>
+    </row>
+    <row r="51" ht="40" customHeight="1">
+      <c r="A51" s="19" t="inlineStr"/>
+      <c r="B51" s="70" t="inlineStr">
+        <is>
+          <t>RecordingService</t>
+        </is>
+      </c>
+      <c r="C51" s="19" t="inlineStr">
+        <is>
+          <t>playback_mutex_</t>
+        </is>
+      </c>
+      <c r="D51" s="19" t="inlineStr">
+        <is>
+          <t>playback_sessions_ map</t>
+        </is>
+      </c>
+      <c r="E51" s="19" t="inlineStr">
+        <is>
+          <t>Independent</t>
+        </is>
+      </c>
+      <c r="F51" s="19" t="inlineStr"/>
+    </row>
+    <row r="52" ht="40" customHeight="1">
+      <c r="A52" s="16" t="inlineStr"/>
+      <c r="B52" s="69" t="inlineStr">
+        <is>
+          <t>FtpManager</t>
+        </is>
+      </c>
+      <c r="C52" s="16" t="inlineStr">
+        <is>
+          <t>mutex_</t>
+        </is>
+      </c>
+      <c r="D52" s="16" t="inlineStr">
+        <is>
+          <t>config_, stats_, callbacks</t>
+        </is>
+      </c>
+      <c r="E52" s="16" t="inlineStr">
+        <is>
+          <t>mutex_ → queue_mutex_ (in GetStats)</t>
+        </is>
+      </c>
+      <c r="F52" s="16" t="inlineStr"/>
+    </row>
+    <row r="53" ht="40" customHeight="1">
+      <c r="A53" s="19" t="inlineStr"/>
+      <c r="B53" s="70" t="inlineStr">
+        <is>
+          <t>FtpManager</t>
+        </is>
+      </c>
+      <c r="C53" s="19" t="inlineStr">
+        <is>
+          <t>queue_mutex_</t>
+        </is>
+      </c>
+      <c r="D53" s="19" t="inlineStr">
+        <is>
+          <t>upload_queue_, upload_history_</t>
+        </is>
+      </c>
+      <c r="E53" s="19" t="inlineStr">
+        <is>
+          <t>Must be acquired AFTER mutex_ if both needed</t>
+        </is>
+      </c>
+      <c r="F53" s="19" t="inlineStr">
+        <is>
+          <t>UploadWorker reads config_ under queue_mutex_ only — Risk R6</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="40" customHeight="1">
+      <c r="A54" s="16" t="inlineStr"/>
+      <c r="B54" s="69" t="inlineStr">
+        <is>
+          <t>NasManager</t>
+        </is>
+      </c>
+      <c r="C54" s="16" t="inlineStr">
+        <is>
+          <t>mutex_</t>
+        </is>
+      </c>
+      <c r="D54" s="16" t="inlineStr">
+        <is>
+          <t>config_, initialized_, mount state</t>
+        </is>
+      </c>
+      <c r="E54" s="16" t="inlineStr">
+        <is>
+          <t>None — sole lock in class</t>
+        </is>
+      </c>
+      <c r="F54" s="16" t="inlineStr">
+        <is>
+          <t>TestConnection() writes config_ without lock — Risk R5</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  KNOWN RESIDUAL RISKS</t>
+        </is>
+      </c>
+      <c r="B56" s="7" t="n"/>
+      <c r="C56" s="7" t="n"/>
+      <c r="D56" s="7" t="n"/>
+      <c r="E56" s="7" t="n"/>
+      <c r="F56" s="8" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="6" t="inlineStr"/>
+      <c r="B57" s="6" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="C57" s="6" t="inlineStr">
+        <is>
+          <t>Module</t>
+        </is>
+      </c>
+      <c r="D57" s="6" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="E57" s="6" t="inlineStr">
+        <is>
+          <t>Severity</t>
+        </is>
+      </c>
+      <c r="F57" s="6" t="inlineStr">
+        <is>
+          <t>Recommended Fix</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="65" customHeight="1">
+      <c r="A58" s="59" t="inlineStr"/>
+      <c r="B58" s="72" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="C58" s="59" t="inlineStr">
+        <is>
+          <t>AnalyticsEngine</t>
+        </is>
+      </c>
+      <c r="D58" s="59" t="inlineStr">
+        <is>
+          <t>audio_event_callback_ is fired while mutex_ is held. If the callback calls any AnalyticsEngine API, deadlock occurs. All other 7 callbacks correctly release the lock first.</t>
+        </is>
+      </c>
+      <c r="E58" s="73" t="inlineStr">
+        <is>
+          <t>Medium
+(deadlock if callback re-enters)</t>
+        </is>
+      </c>
+      <c r="F58" s="59" t="inlineStr">
+        <is>
+          <t>Move audio callback invocation outside the lock scope, identical to detection_callback_ pattern.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="65" customHeight="1">
+      <c r="A59" s="19" t="inlineStr"/>
+      <c r="B59" s="74" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="C59" s="19" t="inlineStr">
+        <is>
+          <t>EventManager</t>
+        </is>
+      </c>
+      <c r="D59" s="19" t="inlineStr">
+        <is>
+          <t>Detached action threads capture 'this' (EventManager pointer). If EventManager is destroyed while a detached thread is still in handler-&gt;Execute(), the subsequent stats_mutex_ access is use-after-free.</t>
+        </is>
+      </c>
+      <c r="E59" s="75" t="inlineStr">
+        <is>
+          <t>Low
+(singleton lives for process lifetime)</t>
+        </is>
+      </c>
+      <c r="F59" s="19" t="inlineStr">
+        <is>
+          <t>Track outstanding threads with atomic counter; drain in Shutdown(). Or capture std::shared_ptr&lt;EventManager&gt;.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="65" customHeight="1">
+      <c r="A60" s="59" t="inlineStr"/>
+      <c r="B60" s="72" t="inlineStr">
+        <is>
+          <t>R3</t>
+        </is>
+      </c>
+      <c r="C60" s="59" t="inlineStr">
+        <is>
+          <t>EventManager</t>
+        </is>
+      </c>
+      <c r="D60" s="59" t="inlineStr">
+        <is>
+          <t>MatchRules() returns std::vector&lt;const EventRule*&gt; pointing into rules_ vector. After the lock releases, a concurrent AddRule/DeleteRule can reallocate the vector, causing dangling pointer dereference in ExecuteActions().</t>
+        </is>
+      </c>
+      <c r="E60" s="73" t="inlineStr">
+        <is>
+          <t>Medium
+(rare — rule changes at runtime)</t>
+        </is>
+      </c>
+      <c r="F60" s="59" t="inlineStr">
+        <is>
+          <t>Return std::vector&lt;EventRule&gt; by value from MatchRules() instead of raw pointers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="65" customHeight="1">
+      <c r="A61" s="19" t="inlineStr"/>
+      <c r="B61" s="74" t="inlineStr">
+        <is>
+          <t>R4</t>
+        </is>
+      </c>
+      <c r="C61" s="19" t="inlineStr">
+        <is>
+          <t>EventManager</t>
+        </is>
+      </c>
+      <c r="D61" s="19" t="inlineStr">
+        <is>
+          <t>PublishEvent() reads config_.queue_max_size and AddToHistory() reads config_.max_history_size without holding config_mutex_. SetConfig() writes these under the lock — a formal C++ data race.</t>
+        </is>
+      </c>
+      <c r="E61" s="75" t="inlineStr">
+        <is>
+          <t>Low
+(int reads are effectively atomic on ARM)</t>
+        </is>
+      </c>
+      <c r="F61" s="19" t="inlineStr">
+        <is>
+          <t>Cache as std::atomic&lt;int&gt;, or snapshot config fields under lock at start of PublishEvent().</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="65" customHeight="1">
+      <c r="A62" s="16" t="inlineStr"/>
+      <c r="B62" s="76" t="inlineStr">
+        <is>
+          <t>R5</t>
+        </is>
+      </c>
+      <c r="C62" s="16" t="inlineStr">
+        <is>
+          <t>NasManager</t>
+        </is>
+      </c>
+      <c r="D62" s="16" t="inlineStr">
+        <is>
+          <t>TestConnection(nullptr) writes config_.last_error and config_.status at lines ~179-180 without holding mutex_. Concurrent GetConfig() / SetConfig() create a data race.</t>
+        </is>
+      </c>
+      <c r="E62" s="77" t="inlineStr">
+        <is>
+          <t>Low
+(test operation, not on hot path)</t>
+        </is>
+      </c>
+      <c r="F62" s="16" t="inlineStr">
+        <is>
+          <t>Hold mutex_ for the full duration of TestConnection when config==nullptr.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="65" customHeight="1">
+      <c r="A63" s="19" t="inlineStr"/>
+      <c r="B63" s="74" t="inlineStr">
+        <is>
+          <t>R6</t>
+        </is>
+      </c>
+      <c r="C63" s="19" t="inlineStr">
+        <is>
+          <t>FtpManager</t>
+        </is>
+      </c>
+      <c r="D63" s="19" t="inlineStr">
+        <is>
+          <t>UploadWorker() reads config_.upload_schedule and config_.enabled while holding only queue_mutex_. SetConfig() holds mutex_, so these reads race with concurrent config changes.</t>
+        </is>
+      </c>
+      <c r="E63" s="75" t="inlineStr">
+        <is>
+          <t>Low
+(upload scheduler, not on hot path)</t>
+        </is>
+      </c>
+      <c r="F63" s="19" t="inlineStr">
+        <is>
+          <t>Snapshot relevant config fields under mutex_ at the start of each worker iteration.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="65" customHeight="1">
+      <c r="A64" s="16" t="inlineStr"/>
+      <c r="B64" s="76" t="inlineStr">
+        <is>
+          <t>R7</t>
+        </is>
+      </c>
+      <c r="C64" s="16" t="inlineStr">
+        <is>
+          <t>IRControl</t>
+        </is>
+      </c>
+      <c r="D64" s="16" t="inlineStr">
+        <is>
+          <t>SwCdsDetectionLoop() reads is_night_mode_ and auto_settings_.mode without g_mutex after the wait_for lock releases. Both are plain non-atomic fields written under g_mutex by other threads — formally a C++ data race.</t>
+        </is>
+      </c>
+      <c r="E64" s="77" t="inlineStr">
+        <is>
+          <t>Low
+(read-only check, worst case: one missed transition)</t>
+        </is>
+      </c>
+      <c r="F64" s="16" t="inlineStr">
+        <is>
+          <t>Make is_night_mode_ std::atomic&lt;bool&gt; and auto_settings_.mode std::atomic&lt;DayNightAutoMode&gt;.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="65" customHeight="1">
+      <c r="A65" s="19" t="inlineStr"/>
+      <c r="B65" s="74" t="inlineStr">
+        <is>
+          <t>R8</t>
+        </is>
+      </c>
+      <c r="C65" s="19" t="inlineStr">
+        <is>
+          <t>EventManager</t>
+        </is>
+      </c>
+      <c r="D65" s="19" t="inlineStr">
+        <is>
+          <t>Init() and Start() check initialized_/running_ with load() then set them separately — a TOCTOU window. Two concurrent Init() calls could both pass the guard.</t>
+        </is>
+      </c>
+      <c r="E65" s="75" t="inlineStr">
+        <is>
+          <t>Very Low
+(Init() only called from main during single-threaded startup)</t>
+        </is>
+      </c>
+      <c r="F65" s="19" t="inlineStr">
+        <is>
+          <t>Use initialized_.exchange(true) to atomically check-and-set.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A36:F36"/>
+    <mergeCell ref="B1:J1"/>
+    <mergeCell ref="A56:F56"/>
+    <mergeCell ref="A21:F21"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/docs/architecture/eterna_ipcamera_architecture.xlsx
+++ b/docs/architecture/eterna_ipcamera_architecture.xlsx
@@ -15,6 +15,7 @@
     <sheet name="Configuration" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="Singleton Inventory" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="Concurrency &amp; Safety" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Design &amp; Optimisation" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Overview'!$A$1:$H$28</definedName>
@@ -26,7 +27,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -150,8 +151,14 @@
       <color rgb="0027AE60"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="19">
+  <fills count="22">
     <fill>
       <patternFill/>
     </fill>
@@ -243,6 +250,21 @@
         <fgColor rgb="00922B21"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001A5276"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D5F5E3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001A8C4E"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="7">
     <border>
@@ -319,7 +341,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="78">
+  <cellXfs count="94">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -540,6 +562,54 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="20" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="20" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -6786,4 +6856,999 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="001A5276"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D54"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="B1" s="78" t="inlineStr">
+        <is>
+          <t>Design Practices &amp; Optimisation Review</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="B2" s="79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  STRONG DESIGN PRACTICES</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="18" customHeight="1">
+      <c r="A3" s="80" t="inlineStr"/>
+      <c r="B3" s="80" t="inlineStr">
+        <is>
+          <t>Practice</t>
+        </is>
+      </c>
+      <c r="C3" s="80" t="inlineStr">
+        <is>
+          <t>Evidence in codebase</t>
+        </is>
+      </c>
+      <c r="D3" s="80" t="inlineStr">
+        <is>
+          <t>Benefit</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="55" customHeight="1">
+      <c r="A4" s="81" t="inlineStr"/>
+      <c r="B4" s="82" t="inlineStr">
+        <is>
+          <t>RAII — all C handles wrapped</t>
+        </is>
+      </c>
+      <c r="C4" s="81" t="inlineStr">
+        <is>
+          <t>VideoRingBuffer destructor: hd_common_mem_free or std::free.
+Statement::~Statement(): sqlite3_finalize().
+Database::~Database(): sqlite3_close().
+FirmwareValidator::Impl::~Impl(): EVP_PKEY_free().
+AudioFrameConsumer destructor: UnregisterConsumer().
+VideoFrameConsumer (unique_ptr): decrements consumer_count.</t>
+        </is>
+      </c>
+      <c r="D4" s="81" t="inlineStr">
+        <is>
+          <t>No resource leaks regardless of execution path.
+Exception-safe — destructor runs even on early return.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="55" customHeight="1">
+      <c r="A5" s="45" t="inlineStr"/>
+      <c r="B5" s="83" t="inlineStr">
+        <is>
+          <t>Pimpl idiom for vendor-heavy classes</t>
+        </is>
+      </c>
+      <c r="C5" s="45" t="inlineStr">
+        <is>
+          <t>UpgradeManager, RtspServer, AacCodec, UserManager, PhysicalMemory,
+FirmwareValidator, SystemController — all use unique_ptr&lt;Impl&gt;.
+Vendor/platform headers confined to .cpp files.</t>
+        </is>
+      </c>
+      <c r="D5" s="45" t="inlineStr">
+        <is>
+          <t>Recompilation cascades avoided when vendor SDK changes.
+Clean public headers with no vendor type pollution.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="55" customHeight="1">
+      <c r="A6" s="81" t="inlineStr"/>
+      <c r="B6" s="82" t="inlineStr">
+        <is>
+          <t>Move semantics — noexcept move constructors</t>
+        </is>
+      </c>
+      <c r="C6" s="81" t="inlineStr">
+        <is>
+          <t>VideoFrameConsumer, MP4Recorder, Database, Statement all have
+noexcept move ctors that move raw handles and std::move string/vector members.
+Callbacks stored with std::move(callback) everywhere.
+Event dequeued with std::move(event_queue_.front()).</t>
+        </is>
+      </c>
+      <c r="D6" s="81" t="inlineStr">
+        <is>
+          <t>Zero-copy ownership transfer of large objects.
+Avoids unnecessary deep copies of std::function and std::vector.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="55" customHeight="1">
+      <c r="A7" s="45" t="inlineStr"/>
+      <c r="B7" s="83" t="inlineStr">
+        <is>
+          <t>Tiered error handling (no exception propagation)</t>
+        </is>
+      </c>
+      <c r="C7" s="45" t="inlineStr">
+        <is>
+          <t>Result&lt;T&gt;/Result&lt;void&gt;: internal business logic.
+std::optional&lt;T&gt;: read operations with no value.
+Expected&lt;T,E&gt; (C++17 polyfill): firmware upgrade pipeline.
+try/catch at webserver boundary only — converted to HTTP status + JSON.</t>
+        </is>
+      </c>
+      <c r="D7" s="45" t="inlineStr">
+        <is>
+          <t>Predictable control flow; no surprise stack unwinds.
+API boundary always returns structured, client-consumable errors.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="55" customHeight="1">
+      <c r="A8" s="81" t="inlineStr"/>
+      <c r="B8" s="82" t="inlineStr">
+        <is>
+          <t>Conditional compilation for portability</t>
+        </is>
+      </c>
+      <c r="C8" s="81" t="inlineStr">
+        <is>
+          <t>HDAL_PIPELINE_ENABLED: all Novatek SDK calls behind guard;
+  stub paths let the same binary build on a developer laptop.
+RTSP_SERVER_ENABLED: Live555 isolated behind guard.
+MQTT_ENABLED: Paho MQTT client conditional.
+OPENSSL_AVAILABLE: RSA key material guarded.</t>
+        </is>
+      </c>
+      <c r="D8" s="81" t="inlineStr">
+        <is>
+          <t>Single codebase runs on both target hardware and host for testing.
+Missing optional dependencies do not break the build.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="55" customHeight="1">
+      <c r="A9" s="45" t="inlineStr"/>
+      <c r="B9" s="83" t="inlineStr">
+        <is>
+          <t>constexpr for all hardware-sizing constants</t>
+        </is>
+      </c>
+      <c r="C9" s="45" t="inlineStr">
+        <is>
+          <t>kVideoRingBufferSlots=30, kMaxVideoFrameSize=512KB,
+kMaxSubStreamFrameSize=128KB, kVideoPullTimeoutMs=100,
+kAudioRingBufferSlots=256, kMaxAudioFrameSize=8192,
+kMaxNalParamSize=256; all filesystem paths in paths.h as constexpr.</t>
+        </is>
+      </c>
+      <c r="D9" s="45" t="inlineStr">
+        <is>
+          <t>Zero runtime cost. Compiler can optimise for exact sizes.
+Single source of truth — change one constant, all uses update.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="55" customHeight="1">
+      <c r="A10" s="81" t="inlineStr"/>
+      <c r="B10" s="82" t="inlineStr">
+        <is>
+          <t>Coordinator pattern — no circular module dependencies</t>
+        </is>
+      </c>
+      <c r="C10" s="81" t="inlineStr">
+        <is>
+          <t>main.cpp is the only place that cross-wires modules:
+  analytics callbacks → EventManager publish methods.
+  HdalPipeline encoder paths → MediaHub constructor.
+No module #includes another module's singleton header.</t>
+        </is>
+      </c>
+      <c r="D10" s="81" t="inlineStr">
+        <is>
+          <t>Clean DAG dependency graph — each module can be built and tested independently.
+Startup order is explicit and all in one place.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="B12" s="84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  PERFORMANCE OPTIMISATIONS</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="80" t="inlineStr"/>
+      <c r="B13" s="80" t="inlineStr">
+        <is>
+          <t>Optimisation</t>
+        </is>
+      </c>
+      <c r="C13" s="80" t="inlineStr">
+        <is>
+          <t>Implementation detail</t>
+        </is>
+      </c>
+      <c r="D13" s="80" t="inlineStr">
+        <is>
+          <t>Impact</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="55" customHeight="1">
+      <c r="A14" s="81" t="inlineStr"/>
+      <c r="B14" s="82" t="inlineStr">
+        <is>
+          <t>Lock-free SPMC ring buffer</t>
+        </is>
+      </c>
+      <c r="C14" s="81" t="inlineStr">
+        <is>
+          <t>Seqlock-style atomic&lt;uint64_t&gt; version per slot (odd=writing, even=ready).
+memory_order_release/acquire pair for happens-before without mutex.
+Double version check (before + after memcpy) catches mid-copy overwrites.
+30 slots per channel = 1 second of video at 30 fps.</t>
+        </is>
+      </c>
+      <c r="D14" s="81" t="inlineStr">
+        <is>
+          <t>Zero mutex overhead on the read path (RTSP, recording, WebRTC).
+Allows unlimited consumers to read the same frame concurrently.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="55" customHeight="1">
+      <c r="A15" s="45" t="inlineStr"/>
+      <c r="B15" s="83" t="inlineStr">
+        <is>
+          <t>Cache-line alignment on shared atomics</t>
+        </is>
+      </c>
+      <c r="C15" s="45" t="inlineStr">
+        <is>
+          <t>alignas(64) on both write_pos_ and frames_written_ in VideoRingBuffer.
+Producer writes write_pos_ every frame;
+consumers read frames_written_ every frame — on separate cache lines.</t>
+        </is>
+      </c>
+      <c r="D15" s="45" t="inlineStr">
+        <is>
+          <t>Eliminates false sharing on multi-core SoC.
+Avoids cache-line ping-pong on every frame at 120 writes/sec (4 channels × 30 fps).</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="55" customHeight="1">
+      <c r="A16" s="81" t="inlineStr"/>
+      <c r="B16" s="82" t="inlineStr">
+        <is>
+          <t>DMA-capable physically-contiguous memory pool</t>
+        </is>
+      </c>
+      <c r="C16" s="81" t="inlineStr">
+        <is>
+          <t>Single hd_common_mem_alloc() at MediaHub::Initialize().
+Encoder output buffer mmap'd at startup; NAL data accessed via
+pointer arithmetic (vir_addr + phy_addr_offset) — near-zero-copy.
+Falls back to std::malloc for non-HDAL builds.</t>
+        </is>
+      </c>
+      <c r="D16" s="81" t="inlineStr">
+        <is>
+          <t>Eliminates per-frame heap allocation and fragmentation.
+DMA-capable memory allows direct kernel→user frame transfer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="55" customHeight="1">
+      <c r="A17" s="45" t="inlineStr"/>
+      <c r="B17" s="83" t="inlineStr">
+        <is>
+          <t>thread_local frame assembly buffer</t>
+        </is>
+      </c>
+      <c r="C17" s="45" t="inlineStr">
+        <is>
+          <t>In ProducerThread: thread_local std::vector&lt;uint8_t&gt; frame_buffer;
+frame_buffer.clear(); frame_buffer.reserve(total_size);
+Capacity grows to max frame size after first large keyframe and never shrinks.</t>
+        </is>
+      </c>
+      <c r="D17" s="45" t="inlineStr">
+        <is>
+          <t>Zero heap allocations on the producer hot path after warm-up.
+Each channel thread has its own buffer — no sharing or locking.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="55" customHeight="1">
+      <c r="A18" s="81" t="inlineStr"/>
+      <c r="B18" s="82" t="inlineStr">
+        <is>
+          <t>Hardware timestamp for RTP — one syscall per stream</t>
+        </is>
+      </c>
+      <c r="C18" s="81" t="inlineStr">
+        <is>
+          <t>HDAL hw encoder tick (data_pull.timestamp, µs resolution) stored in every slot.
+RTP presentation time = base_wall_time + (hw_delta from base_hw_timestamp).
+gettimeofday() called exactly once per stream lifetime (at first frame).
+Sanity re-anchor on implausible deltas (&gt;10 s, backward jump, wrap).</t>
+        </is>
+      </c>
+      <c r="D18" s="81" t="inlineStr">
+        <is>
+          <t>Eliminates gettimeofday() on every frame (~120 calls/sec avoided).
+RTP timestamps are jitter-free even under scheduler latency.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="55" customHeight="1">
+      <c r="A19" s="45" t="inlineStr"/>
+      <c r="B19" s="83" t="inlineStr">
+        <is>
+          <t>Narrow lock scope / snapshot pattern</t>
+        </is>
+      </c>
+      <c r="C19" s="45" t="inlineStr">
+        <is>
+          <t>RecordingService: ch_config = config_.channels[ch] under lock; long loop uses copy.
+SetConfig(): assigns under lock, then calls SaveConfig() outside lock.
+AnalyticsEngine: stats copied in one lock_guard; callbacks fired outside.
+EventManager: listener list copied under lock; iterated outside.</t>
+        </is>
+      </c>
+      <c r="D19" s="45" t="inlineStr">
+        <is>
+          <t>Lock held for microseconds, not milliseconds of I/O or callbacks.
+File writes, HDAL calls, and network operations never block other threads.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="55" customHeight="1">
+      <c r="A20" s="81" t="inlineStr"/>
+      <c r="B20" s="82" t="inlineStr">
+        <is>
+          <t>reserve() for hot-path vectors</t>
+        </is>
+      </c>
+      <c r="C20" s="81" t="inlineStr">
+        <is>
+          <t>aac_output_buffer.reserve(AacCodec::kMaxOutputSize) — once per recording session.
+nal_packs.reserve(data_pull.pack_num) — per frame in producer.
+RTSP send buffer: kSendBufferSize = 8 MB set on socket once.</t>
+        </is>
+      </c>
+      <c r="D20" s="81" t="inlineStr">
+        <is>
+          <t>Vector reallocation eliminated after first frame.
+Predictable memory footprint — no surprise allocations mid-session.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="55" customHeight="1">
+      <c r="A21" s="45" t="inlineStr"/>
+      <c r="B21" s="83" t="inlineStr">
+        <is>
+          <t>Delta-only config persistence</t>
+        </is>
+      </c>
+      <c r="C21" s="45" t="inlineStr">
+        <is>
+          <t>config::Save() diffs g_config_tree vs g_factory_tree.
+Only changed keys written to config.json (~hundreds of bytes).
+Empty delta → config.json deleted (factory defaults on next boot).
+Atomic rename() ensures no partial-write on power loss.</t>
+        </is>
+      </c>
+      <c r="D21" s="45" t="inlineStr">
+        <is>
+          <t>Flash write amplification minimised — one changed int ≠ 50 KB write.
+Factory reset is one file delete, no re-flash.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="55" customHeight="1">
+      <c r="A22" s="81" t="inlineStr"/>
+      <c r="B22" s="82" t="inlineStr">
+        <is>
+          <t>Interruptible sleep for fast shutdown</t>
+        </is>
+      </c>
+      <c r="C22" s="81" t="inlineStr">
+        <is>
+          <t>IRControl loops: cv.wait_for(lock, 1s/30s, stop_flag predicate).
+FtpManager worker: cv.wait_for(lock, 60s, shutdown || !queue_empty).
+RecordingService monitor: 50 × 100ms slices, atomic flag checked each.
+notify_all() in every Shutdown() wakes threads immediately.</t>
+        </is>
+      </c>
+      <c r="D22" s="81" t="inlineStr">
+        <is>
+          <t>Shutdown latency bounded to &lt;100 ms instead of up to 60 s.
+No threads blocking shutdown — _Exit(0) reached promptly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="B24" s="85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  AREAS FOR IMPROVEMENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="80" t="inlineStr"/>
+      <c r="B25" s="80" t="inlineStr">
+        <is>
+          <t>Issue</t>
+        </is>
+      </c>
+      <c r="C25" s="80" t="inlineStr">
+        <is>
+          <t>Detail &amp; Location</t>
+        </is>
+      </c>
+      <c r="D25" s="80" t="inlineStr">
+        <is>
+          <t>Recommended Fix</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="65" customHeight="1">
+      <c r="A26" s="59" t="inlineStr"/>
+      <c r="B26" s="86" t="inlineStr">
+        <is>
+          <t>No test coverage for 5 of 11 modules</t>
+        </is>
+      </c>
+      <c r="C26" s="59" t="inlineStr">
+        <is>
+          <t>modules/platform, modules/ai, modules/streaming, modules/recording,
+modules/webserver — zero test source files.
+modules/events is well covered (unit + integration + stress).
+modules/media, config, storage, networking — partial only.</t>
+        </is>
+      </c>
+      <c r="D26" s="59" t="inlineStr">
+        <is>
+          <t>Priority: media/ (ring buffer), recording/ (MP4 segment correctness),
+webserver/ (REST contract regression). Add a GoogleTest or Catch2 suite.
+Mock HDAL with HDAL_PIPELINE_ENABLED=0 stub for host-machine CI.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="65" customHeight="1">
+      <c r="A27" s="59" t="inlineStr"/>
+      <c r="B27" s="86" t="inlineStr">
+        <is>
+          <t>TLS peer verification disabled in WebhookHandler</t>
+        </is>
+      </c>
+      <c r="C27" s="59" t="inlineStr">
+        <is>
+          <t>modules/events/src/actions/webhook_action.cpp ~line 72:
+CURLOPT_SSL_VERIFYPEER hardcoded to 0L.
+All outbound webhooks accept any certificate — MITM attack surface.</t>
+        </is>
+      </c>
+      <c r="D27" s="59" t="inlineStr">
+        <is>
+          <t>Enable CURLOPT_SSL_VERIFYPEER = 1L (default).
+Bundle a CA bundle path (CURLOPT_CAINFO) or use system cert store.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="65" customHeight="1">
+      <c r="A28" s="59" t="inlineStr"/>
+      <c r="B28" s="86" t="inlineStr">
+        <is>
+          <t>config::Set() has no value validation</t>
+        </is>
+      </c>
+      <c r="C28" s="59" t="inlineStr">
+        <is>
+          <t>Any call can write Set&lt;int&gt;("ir.led.brightness", 9999).
+Validation only at each use site — manual config.json edits bypass it.
+ConfigLoader (YAML path) already has per-subsystem validators.</t>
+        </is>
+      </c>
+      <c r="D28" s="59" t="inlineStr">
+        <is>
+          <t>Add RegisterValidator(path_prefix, ValidatorFn) to the JSON config module,
+mirroring validateNetworkConfig/validateStorageConfig in ConfigLoader.
+Call validators in Set() and in Init() after loading user delta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="65" customHeight="1">
+      <c r="A29" s="33" t="inlineStr"/>
+      <c r="B29" s="87" t="inlineStr">
+        <is>
+          <t>audio_event_callback_ fired while mutex_ is held (AnalyticsEngine)</t>
+        </is>
+      </c>
+      <c r="C29" s="33" t="inlineStr">
+        <is>
+          <t>modules/ai/src/analytics.cpp ~line 2558.
+All 7 other callbacks release mutex_ before invocation.
+If audio callback calls GetStats() or SetConfig() → deadlock.</t>
+        </is>
+      </c>
+      <c r="D29" s="33" t="inlineStr">
+        <is>
+          <t>Move audio callback invocation outside the lock scope.
+Pattern is established in detection_callback_, motion_callback_, etc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="65" customHeight="1">
+      <c r="A30" s="33" t="inlineStr"/>
+      <c r="B30" s="87" t="inlineStr">
+        <is>
+          <t>MatchRules() returns raw pointers into rules_ vector (EventManager)</t>
+        </is>
+      </c>
+      <c r="C30" s="33" t="inlineStr">
+        <is>
+          <t>modules/events/src/event_manager.cpp ~line 769.
+vector&lt;const EventRule*&gt; returned after rules_mutex_ is released.
+Concurrent AddRule/DeleteRule can reallocate the vector → dangling pointer
+dereference in ExecuteActions().</t>
+        </is>
+      </c>
+      <c r="D30" s="33" t="inlineStr">
+        <is>
+          <t>Return std::vector&lt;EventRule&gt; by value from MatchRules().
+Small copy (each rule is a config struct) — negligible overhead.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="65" customHeight="1">
+      <c r="A31" s="33" t="inlineStr"/>
+      <c r="B31" s="87" t="inlineStr">
+        <is>
+          <t>OsdOverlay uses printf instead of spdlog</t>
+        </is>
+      </c>
+      <c r="C31" s="33" t="inlineStr">
+        <is>
+          <t>modules/platform/src/osd_overlay.cpp — ~30 printf() calls, zero spdlog.
+OSD log output is invisible to log files and remote syslog.</t>
+        </is>
+      </c>
+      <c r="D31" s="33" t="inlineStr">
+        <is>
+          <t>Replace all printf('[OSD] ...') with spdlog::debug/error('[OSD] ...').
+One-time 30-line find-and-replace.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="65" customHeight="1">
+      <c r="A32" s="33" t="inlineStr"/>
+      <c r="B32" s="87" t="inlineStr">
+        <is>
+          <t>Duplicate VideoControl::Init() in main.cpp</t>
+        </is>
+      </c>
+      <c r="C32" s="33" t="inlineStr">
+        <is>
+          <t>Called at line ~357 (early startup) and again at line ~751.
+Second call is a silent no-op today (guarded by if(initialized_) return true),
+but obscures whether the early init actually succeeded.</t>
+        </is>
+      </c>
+      <c r="D32" s="33" t="inlineStr">
+        <is>
+          <t>Remove the duplicate call at line ~751.
+Add a spdlog::warn if Init() is called when already initialized.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="65" customHeight="1">
+      <c r="A33" s="33" t="inlineStr"/>
+      <c r="B33" s="87" t="inlineStr">
+        <is>
+          <t>Vendor headers leak into public hdal_pipeline.h</t>
+        </is>
+      </c>
+      <c r="C33" s="33" t="inlineStr">
+        <is>
+          <t>6 Novatek vendor headers (hdal.h, vendor_isp.h, etc.) included in the
+public interface when HDAL_PIPELINE_ENABLED is set.
+HD_PATH_ID, HD_DIM, HD_VIDEOCAP_SYSCAPS appear in private member declarations.</t>
+        </is>
+      </c>
+      <c r="D33" s="33" t="inlineStr">
+        <is>
+          <t>Apply Pimpl idiom to HdalPipeline:
+move all HDAL-typed private members into struct Impl in hdal_pipeline_impl.cpp.
+Public header exposes only the high-level API with no vendor types.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="65" customHeight="1">
+      <c r="A34" s="19" t="inlineStr"/>
+      <c r="B34" s="70" t="inlineStr">
+        <is>
+          <t>Missing std::string_view on hot-path string parameters</t>
+        </is>
+      </c>
+      <c r="C34" s="19" t="inlineStr">
+        <is>
+          <t>All string parameters use const std::string&amp; throughout.
+config::Get&lt;T&gt;(path, default) called on every frame for some paths —
+string literal arguments cause implicit std::string construction.</t>
+        </is>
+      </c>
+      <c r="D34" s="19" t="inlineStr">
+        <is>
+          <t>Adopt std::string_view for read-only string parameters in:
+config::Get/Set/Has, MediaHub::CreateConsumer, EventManager::AddListener.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="65" customHeight="1">
+      <c r="A35" s="19" t="inlineStr"/>
+      <c r="B35" s="70" t="inlineStr">
+        <is>
+          <t>Magic numbers in analytics.cpp and media_hub.cpp</t>
+        </is>
+      </c>
+      <c r="C35" s="19" t="inlineStr">
+        <is>
+          <t>analytics.cpp: tamper VQA resolution 320,180; defocus threshold 100.0f;
+  mosaic block_size=16, blur_radius=21, denoise_strength=50.
+media_hub.cpp: HD sub-stream cap 256*1024 (unnamed, between the two named consts).</t>
+        </is>
+      </c>
+      <c r="D35" s="19" t="inlineStr">
+        <is>
+          <t>Add constexpr names: kVqaWidth/kVqaHeight, kDefocusThreshold,
+kMosaicBlockSize, kMaxHdSubStreamFrameSize.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="65" customHeight="1">
+      <c r="A36" s="19" t="inlineStr"/>
+      <c r="B36" s="70" t="inlineStr">
+        <is>
+          <t>Known stubs / unimplemented features</t>
+        </is>
+      </c>
+      <c r="C36" s="19" t="inlineStr">
+        <is>
+          <t>AnalyticsEngine::ProcessFrame() — empty stub (TODO: Process frame through AI models).
+Snapshot REST endpoint — returns HTTP 503.
+Firmware upgrade from URL — returns error.
+WiFi scan/connect/forget/power — 5 methods return Err('not implemented').
+ONVIF recording job count — always returns 0.
+OP-TEE key derivation — placeholder comment in storage.cpp.</t>
+        </is>
+      </c>
+      <c r="D36" s="19" t="inlineStr">
+        <is>
+          <t>Track in issue tracker with owner per item.
+Until implemented, ensure stubs return clear HTTP 501 Not Implemented
+rather than 500/503 to distinguish 'planned' from 'error'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="20" customHeight="1">
+      <c r="B38" s="79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  SUMMARY SCORECARD</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="18" customHeight="1">
+      <c r="A39" s="80" t="inlineStr"/>
+      <c r="B39" s="80" t="inlineStr">
+        <is>
+          <t>Area</t>
+        </is>
+      </c>
+      <c r="C39" s="80" t="inlineStr">
+        <is>
+          <t>Rating</t>
+        </is>
+      </c>
+      <c r="D39" s="80" t="inlineStr">
+        <is>
+          <t>Key Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="26" customHeight="1">
+      <c r="A40" s="88" t="inlineStr"/>
+      <c r="B40" s="89" t="inlineStr">
+        <is>
+          <t>RAII &amp; resource ownership</t>
+        </is>
+      </c>
+      <c r="C40" s="90" t="inlineStr">
+        <is>
+          <t>✅  Strong</t>
+        </is>
+      </c>
+      <c r="D40" s="88" t="inlineStr">
+        <is>
+          <t>unique_ptr throughout; all C handles (SQLite, HDAL, OpenSSL, curl) have RAII wrappers</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="26" customHeight="1">
+      <c r="A41" s="88" t="inlineStr"/>
+      <c r="B41" s="89" t="inlineStr">
+        <is>
+          <t>Move semantics</t>
+        </is>
+      </c>
+      <c r="C41" s="90" t="inlineStr">
+        <is>
+          <t>✅  Strong</t>
+        </is>
+      </c>
+      <c r="D41" s="88" t="inlineStr">
+        <is>
+          <t>noexcept move ctors; std::move on callbacks, events, config copies</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="26" customHeight="1">
+      <c r="A42" s="88" t="inlineStr"/>
+      <c r="B42" s="89" t="inlineStr">
+        <is>
+          <t>Ring buffer design</t>
+        </is>
+      </c>
+      <c r="C42" s="90" t="inlineStr">
+        <is>
+          <t>✅  Strong</t>
+        </is>
+      </c>
+      <c r="D42" s="88" t="inlineStr">
+        <is>
+          <t>Lock-free SPMC; seqlock versioning; cache-line aligned; DMA memory pool</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="26" customHeight="1">
+      <c r="A43" s="88" t="inlineStr"/>
+      <c r="B43" s="89" t="inlineStr">
+        <is>
+          <t>Error handling</t>
+        </is>
+      </c>
+      <c r="C43" s="90" t="inlineStr">
+        <is>
+          <t>✅  Strong</t>
+        </is>
+      </c>
+      <c r="D43" s="88" t="inlineStr">
+        <is>
+          <t>Tiered Result/optional/Expected; no exception leakage past API boundary</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="26" customHeight="1">
+      <c r="A44" s="88" t="inlineStr"/>
+      <c r="B44" s="89" t="inlineStr">
+        <is>
+          <t>Lock discipline</t>
+        </is>
+      </c>
+      <c r="C44" s="90" t="inlineStr">
+        <is>
+          <t>✅  Good</t>
+        </is>
+      </c>
+      <c r="D44" s="88" t="inlineStr">
+        <is>
+          <t>Narrow scopes; snapshot pattern; 4 explicit deadlock mitigations; callbacks outside locks</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="26" customHeight="1">
+      <c r="A45" s="88" t="inlineStr"/>
+      <c r="B45" s="89" t="inlineStr">
+        <is>
+          <t>Conditional compilation</t>
+        </is>
+      </c>
+      <c r="C45" s="90" t="inlineStr">
+        <is>
+          <t>✅  Good</t>
+        </is>
+      </c>
+      <c r="D45" s="88" t="inlineStr">
+        <is>
+          <t>4 feature guards; same code builds on laptop without HDAL SDK</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="26" customHeight="1">
+      <c r="A46" s="88" t="inlineStr"/>
+      <c r="B46" s="89" t="inlineStr">
+        <is>
+          <t>constexpr constants</t>
+        </is>
+      </c>
+      <c r="C46" s="90" t="inlineStr">
+        <is>
+          <t>✅  Good</t>
+        </is>
+      </c>
+      <c r="D46" s="88" t="inlineStr">
+        <is>
+          <t>All hot-path capacity limits named; no magic numbers in ring buffer/audio paths</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="26" customHeight="1">
+      <c r="A47" s="88" t="inlineStr"/>
+      <c r="B47" s="89" t="inlineStr">
+        <is>
+          <t>Hardware timestamp usage</t>
+        </is>
+      </c>
+      <c r="C47" s="90" t="inlineStr">
+        <is>
+          <t>✅  Good</t>
+        </is>
+      </c>
+      <c r="D47" s="88" t="inlineStr">
+        <is>
+          <t>gettimeofday() once per stream; RTP timestamps derived from HW tick delta</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="26" customHeight="1">
+      <c r="A48" s="31" t="inlineStr"/>
+      <c r="B48" s="32" t="inlineStr">
+        <is>
+          <t>Config validation</t>
+        </is>
+      </c>
+      <c r="C48" s="91" t="inlineStr">
+        <is>
+          <t>⚠️  Weak</t>
+        </is>
+      </c>
+      <c r="D48" s="31" t="inlineStr">
+        <is>
+          <t>Set() accepts any value; no server-side validation at config layer</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="26" customHeight="1">
+      <c r="A49" s="31" t="inlineStr"/>
+      <c r="B49" s="32" t="inlineStr">
+        <is>
+          <t>Logging consistency</t>
+        </is>
+      </c>
+      <c r="C49" s="91" t="inlineStr">
+        <is>
+          <t>⚠️  Weak</t>
+        </is>
+      </c>
+      <c r="D49" s="31" t="inlineStr">
+        <is>
+          <t>OsdOverlay uses printf; all other modules use spdlog</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="26" customHeight="1">
+      <c r="A50" s="31" t="inlineStr"/>
+      <c r="B50" s="32" t="inlineStr">
+        <is>
+          <t>string_view adoption</t>
+        </is>
+      </c>
+      <c r="C50" s="91" t="inlineStr">
+        <is>
+          <t>⚠️  Weak</t>
+        </is>
+      </c>
+      <c r="D50" s="31" t="inlineStr">
+        <is>
+          <t>const std::string&amp; everywhere; implicit constructions on hot paths</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="26" customHeight="1">
+      <c r="A51" s="31" t="inlineStr"/>
+      <c r="B51" s="32" t="inlineStr">
+        <is>
+          <t>Vendor header isolation</t>
+        </is>
+      </c>
+      <c r="C51" s="91" t="inlineStr">
+        <is>
+          <t>⚠️  Weak</t>
+        </is>
+      </c>
+      <c r="D51" s="31" t="inlineStr">
+        <is>
+          <t>hdal_pipeline.h pulls in 6 vendor headers when HDAL_PIPELINE_ENABLED</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="26" customHeight="1">
+      <c r="A52" s="92" t="inlineStr"/>
+      <c r="B52" s="93" t="inlineStr">
+        <is>
+          <t>TLS security</t>
+        </is>
+      </c>
+      <c r="C52" s="61" t="inlineStr">
+        <is>
+          <t>❌  Risk</t>
+        </is>
+      </c>
+      <c r="D52" s="92" t="inlineStr">
+        <is>
+          <t>Webhook handler disables SSL peer verification (CURLOPT_SSL_VERIFYPEER=0)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="26" customHeight="1">
+      <c r="A53" s="92" t="inlineStr"/>
+      <c r="B53" s="93" t="inlineStr">
+        <is>
+          <t>Test coverage</t>
+        </is>
+      </c>
+      <c r="C53" s="61" t="inlineStr">
+        <is>
+          <t>❌  Poor</t>
+        </is>
+      </c>
+      <c r="D53" s="92" t="inlineStr">
+        <is>
+          <t>5 of 11 modules have zero test files; no cross-module integration test suite</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="26" customHeight="1">
+      <c r="A54" s="31" t="inlineStr"/>
+      <c r="B54" s="32" t="inlineStr">
+        <is>
+          <t>Known stubs</t>
+        </is>
+      </c>
+      <c r="C54" s="91" t="inlineStr">
+        <is>
+          <t>⚠️  Present</t>
+        </is>
+      </c>
+      <c r="D54" s="31" t="inlineStr">
+        <is>
+          <t>ProcessFrame() empty; snapshot 503; WiFi unimplemented; OP-TEE placeholder</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="B1:D1"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="B2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>